--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_03/pre_sizing_results_optimized.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_03/pre_sizing_results_optimized.xlsx
@@ -497,2052 +497,2052 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99.99999973206229</v>
+        <v>34.50082615966561</v>
       </c>
       <c r="B2" t="n">
-        <v>39.40996844113356</v>
+        <v>59.94232120113513</v>
       </c>
       <c r="C2" t="n">
-        <v>38.79464539075961</v>
+        <v>39.44045839895245</v>
       </c>
       <c r="D2" t="n">
-        <v>6.836615442961842</v>
+        <v>6.053403072778151</v>
       </c>
       <c r="E2" t="n">
-        <v>4.219555424437986</v>
+        <v>4.915986816386344</v>
       </c>
       <c r="F2" t="n">
-        <v>7.851305320278405</v>
+        <v>2.154356729234808</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003986848084749735</v>
+        <v>0.1634369906930518</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.9611062528320581</v>
+        <v>-0.02080470226882473</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9719518258729997</v>
+        <v>-0.4217613216615316</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.9930643949805192</v>
+        <v>-0.524644410921533</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.0006285362563900822</v>
+        <v>-0.0007399133282450645</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.6220069709925228</v>
+        <v>-0.6531301634979101</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0031050412674367</v>
+        <v>-0.2027736264222382</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>32.7882327231521</v>
+        <v>34.50082615966561</v>
       </c>
       <c r="B3" t="n">
-        <v>60.95090466808845</v>
+        <v>59.94232120113513</v>
       </c>
       <c r="C3" t="n">
-        <v>39.0803974587415</v>
+        <v>39.44045839895245</v>
       </c>
       <c r="D3" t="n">
-        <v>5.012531212287101</v>
+        <v>6.053403072778151</v>
       </c>
       <c r="E3" t="n">
-        <v>4.112772956913566</v>
+        <v>4.974166809131373</v>
       </c>
       <c r="F3" t="n">
-        <v>1.997740930468128</v>
+        <v>2.154356729234808</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2004337360951663</v>
+        <v>0.1634369906930518</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.006290926885428757</v>
+        <v>-0.02080470226882473</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4152666202098958</v>
+        <v>-0.4217613216615316</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.514612026365147</v>
+        <v>-0.524644410921533</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.02118489056665533</v>
+        <v>-0.0007399133282450645</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.671712695491956</v>
+        <v>-0.6531301634979101</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.05830085336409775</v>
+        <v>-0.2027736264222382</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99.99999973206229</v>
+        <v>99.99999999997357</v>
       </c>
       <c r="B4" t="n">
-        <v>48.23957361029133</v>
+        <v>69.92469267705079</v>
       </c>
       <c r="C4" t="n">
-        <v>38.79464539075961</v>
+        <v>38.6632226015829</v>
       </c>
       <c r="D4" t="n">
-        <v>6.836615442961842</v>
+        <v>7.581738508515107</v>
       </c>
       <c r="E4" t="n">
-        <v>4.219555424437986</v>
+        <v>4.488034704150452</v>
       </c>
       <c r="F4" t="n">
-        <v>7.851305320278405</v>
+        <v>7.991956968107693</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003986848084749735</v>
+        <v>0.003930454625084795</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9611062528320581</v>
+        <v>-0.9557051546207525</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9719518258729997</v>
+        <v>-0.9679906907513638</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.9930643949805192</v>
+        <v>-0.9917993954666009</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0006285362563900822</v>
+        <v>-4.55282103360888e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6220069709925228</v>
+        <v>-0.5874999999998117</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0031050412674367</v>
+        <v>-0.02141860703601145</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>39.01733400347842</v>
+        <v>81.2086982560371</v>
       </c>
       <c r="B5" t="n">
-        <v>71.51551158296007</v>
+        <v>113.3519712348826</v>
       </c>
       <c r="C5" t="n">
-        <v>38.8031732795567</v>
+        <v>38.66554813578272</v>
       </c>
       <c r="D5" t="n">
-        <v>5.378094366790728</v>
+        <v>10.5963474226662</v>
       </c>
       <c r="E5" t="n">
-        <v>4.240517021896412</v>
+        <v>4.441361817983118</v>
       </c>
       <c r="F5" t="n">
-        <v>2.437004903540888</v>
+        <v>5.952224440333993</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1038336263486572</v>
+        <v>0.00789875266964883</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.406790184191663</v>
+        <v>-0.9194933453098312</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6158881221540159</v>
+        <v>-0.9432407964936598</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.7548589151418456</v>
+        <v>-0.9821175541662198</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.001497274294328617</v>
+        <v>-0.1215004692914885</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6803851714019641</v>
+        <v>-0.4536119750742643</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.004842311972318359</v>
+        <v>-0.02196123168263592</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>58.7800040947923</v>
+        <v>56.5418000395542</v>
       </c>
       <c r="B6" t="n">
-        <v>198.5129858653132</v>
+        <v>82.0471446937806</v>
       </c>
       <c r="C6" t="n">
-        <v>38.85505388510907</v>
+        <v>38.64455308987452</v>
       </c>
       <c r="D6" t="n">
-        <v>12.25121108223467</v>
+        <v>7.88682382304765</v>
       </c>
       <c r="E6" t="n">
-        <v>3.887670879852688</v>
+        <v>4.561929741236241</v>
       </c>
       <c r="F6" t="n">
-        <v>3.922258932213723</v>
+        <v>3.973143858210932</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02567420201318658</v>
+        <v>0.02652554143209483</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8190032841524589</v>
+        <v>-0.7715763372294154</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8663044009581229</v>
+        <v>-0.8340460530385922</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.9480308042780943</v>
+        <v>-0.9303167988395362</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.06123580202898495</v>
+        <v>-0.1768998231421857</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.3140907293142785</v>
+        <v>-0.6080980669171765</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.01541124155409684</v>
+        <v>-0.01706238763738904</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>87.90658303300731</v>
+        <v>43.06606494274421</v>
       </c>
       <c r="B7" t="n">
-        <v>159.1526783191504</v>
+        <v>52.09336108201614</v>
       </c>
       <c r="C7" t="n">
-        <v>38.8023325148058</v>
+        <v>38.59063468049967</v>
       </c>
       <c r="D7" t="n">
-        <v>10.63045018898639</v>
+        <v>5.104711956121347</v>
       </c>
       <c r="E7" t="n">
-        <v>3.950415664209606</v>
+        <v>4.269532945075783</v>
       </c>
       <c r="F7" t="n">
-        <v>6.720203400530246</v>
+        <v>2.805531741685131</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00616522109034325</v>
+        <v>0.06991614351522896</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9437856725904458</v>
+        <v>-0.4927796559172071</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9594342780223755</v>
+        <v>-0.6630909980524657</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9887912660160325</v>
+        <v>-0.8010607667920642</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3417750796689292</v>
+        <v>-0.03617179192564952</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5316683049773568</v>
+        <v>-0.6932047605975438</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.004671034413924967</v>
+        <v>-0.004481425449923276</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>62.1023133450343</v>
+        <v>41.64223766725377</v>
       </c>
       <c r="B8" t="n">
-        <v>149.417520928747</v>
+        <v>50.46763077506931</v>
       </c>
       <c r="C8" t="n">
-        <v>38.80786596487181</v>
+        <v>38.66306501852485</v>
       </c>
       <c r="D8" t="n">
-        <v>11.69967748266827</v>
+        <v>5.001949855040476</v>
       </c>
       <c r="E8" t="n">
-        <v>4.505281938422785</v>
+        <v>4.667768418731942</v>
       </c>
       <c r="F8" t="n">
-        <v>4.134884098802325</v>
+        <v>2.652090853096182</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02089192616793377</v>
+        <v>0.07930089105596554</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8461134296050865</v>
+        <v>-0.4406835881859762</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.886352313689745</v>
+        <v>-0.6343600609664175</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9580633789998486</v>
+        <v>-0.7739175892518719</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0252261229234968</v>
+        <v>-0.05384684724114455</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.338908611078012</v>
+        <v>-0.3759527309771032</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.005798288875764892</v>
+        <v>-0.02138183765579685</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>39.70638559615124</v>
+        <v>60.38532060351132</v>
       </c>
       <c r="B9" t="n">
-        <v>56.61586144460752</v>
+        <v>65.52971198851255</v>
       </c>
       <c r="C9" t="n">
-        <v>38.92077617896648</v>
+        <v>38.60211627600561</v>
       </c>
       <c r="D9" t="n">
-        <v>5.319965390644153</v>
+        <v>7.607520697283154</v>
       </c>
       <c r="E9" t="n">
-        <v>4.637188755522179</v>
+        <v>4.562812730302581</v>
       </c>
       <c r="F9" t="n">
-        <v>2.506669777723508</v>
+        <v>4.361687886356551</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0970895692519677</v>
+        <v>0.02089199639130637</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4368832358482864</v>
+        <v>-0.8117475978877903</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6322634334955078</v>
+        <v>-0.8621795007303833</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7712167767888065</v>
+        <v>-0.9460017106276279</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.06751080649968393</v>
+        <v>-0.2435525479368725</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6781327194571318</v>
+        <v>-0.6324403638222384</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.02879994988423778</v>
+        <v>-0.007160464401309297</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>40.81083043981361</v>
+        <v>36.43022525386831</v>
       </c>
       <c r="B10" t="n">
-        <v>61.00223656250123</v>
+        <v>58.40549147004327</v>
       </c>
       <c r="C10" t="n">
-        <v>38.80280154717924</v>
+        <v>38.58302405372362</v>
       </c>
       <c r="D10" t="n">
-        <v>5.139132791355705</v>
+        <v>5.98520031917554</v>
       </c>
       <c r="E10" t="n">
-        <v>4.27688319605777</v>
+        <v>4.107929272283143</v>
       </c>
       <c r="F10" t="n">
-        <v>2.575252884913791</v>
+        <v>2.290945538346959</v>
       </c>
       <c r="G10" t="n">
-        <v>0.08745687150355144</v>
+        <v>0.1324892849619811</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4809435311373466</v>
+        <v>-0.1673522059785422</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6566541498594692</v>
+        <v>-0.4924609428387632</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7946315691843153</v>
+        <v>-0.6167017661639885</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.03548333427623249</v>
+        <v>-0.009805010238810532</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6915497909351501</v>
+        <v>-0.6156514403530045</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.004766583994998217</v>
+        <v>-0.002705612535510993</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>95.60843836286561</v>
+        <v>35.64455484407438</v>
       </c>
       <c r="B11" t="n">
-        <v>178.9523008179102</v>
+        <v>58.40014666794944</v>
       </c>
       <c r="C11" t="n">
-        <v>38.81192610550976</v>
+        <v>38.76892755261808</v>
       </c>
       <c r="D11" t="n">
-        <v>7.786087708164218</v>
+        <v>6.03583030352539</v>
       </c>
       <c r="E11" t="n">
-        <v>4.349526248345457</v>
+        <v>4.245190269408377</v>
       </c>
       <c r="F11" t="n">
-        <v>7.364883741675295</v>
+        <v>2.233921350322596</v>
       </c>
       <c r="G11" t="n">
-        <v>0.004618456797761335</v>
+        <v>0.1440947768573786</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9558354245904105</v>
+        <v>-0.1114897333528758</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9680864106970569</v>
+        <v>-0.4651379138467198</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9918209662421248</v>
+        <v>-0.5821958057971433</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.06438854715892715</v>
+        <v>-0.03752219167055217</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5892017013413112</v>
+        <v>-0.609862361081099</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.006625406062192639</v>
+        <v>-0.04608309561088555</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>82.7987281480808</v>
+        <v>84.64911152958135</v>
       </c>
       <c r="B12" t="n">
-        <v>69.12073154068493</v>
+        <v>103.9356170432433</v>
       </c>
       <c r="C12" t="n">
-        <v>38.85487907836326</v>
+        <v>38.58582556344746</v>
       </c>
       <c r="D12" t="n">
-        <v>5.000366838459829</v>
+        <v>9.929500471120162</v>
       </c>
       <c r="E12" t="n">
-        <v>4.027944138205369</v>
+        <v>4.106631817525838</v>
       </c>
       <c r="F12" t="n">
-        <v>6.468504822795654</v>
+        <v>6.271858367598075</v>
       </c>
       <c r="G12" t="n">
-        <v>0.007155060018278355</v>
+        <v>0.006838424356345185</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.9340231738123749</v>
+        <v>-0.9286227086349237</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9534445312651256</v>
+        <v>-0.9492421506467927</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9862969818359624</v>
+        <v>-0.9847279151273404</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.00986056817044636</v>
+        <v>-0.07423961914068448</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.4173625336067806</v>
+        <v>-0.4781249196482671</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.01537563055520385</v>
+        <v>-0.003359298137740885</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>35.03329220942455</v>
+        <v>59.40401048256543</v>
       </c>
       <c r="B13" t="n">
-        <v>59.7703050704943</v>
+        <v>67.92162036639907</v>
       </c>
       <c r="C13" t="n">
-        <v>39.17194764436272</v>
+        <v>38.60211627600561</v>
       </c>
       <c r="D13" t="n">
-        <v>5.349775698425927</v>
+        <v>7.607520697283154</v>
       </c>
       <c r="E13" t="n">
-        <v>4.601532165698167</v>
+        <v>3.912204426214648</v>
       </c>
       <c r="F13" t="n">
-        <v>2.159981946015697</v>
+        <v>4.25089916623345</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1562059037243854</v>
+        <v>0.02215707450934322</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.183390311779761</v>
+        <v>-0.8024800130676879</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5005462683076094</v>
+        <v>-0.855585285699212</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6256564331775981</v>
+        <v>-0.9424752581215252</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.001505425494281287</v>
+        <v>-0.2106001933908644</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6485144209625412</v>
+        <v>-0.6262253997229144</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.06687294883004416</v>
+        <v>-0.007160464401309297</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>64.49961940420857</v>
+        <v>67.68094891908957</v>
       </c>
       <c r="B14" t="n">
-        <v>186.2979084420868</v>
+        <v>141.7084114076137</v>
       </c>
       <c r="C14" t="n">
-        <v>38.80481168102705</v>
+        <v>38.65828631297374</v>
       </c>
       <c r="D14" t="n">
-        <v>11.55346478176276</v>
+        <v>11.43605512504176</v>
       </c>
       <c r="E14" t="n">
-        <v>4.511817442555625</v>
+        <v>4.689485095256241</v>
       </c>
       <c r="F14" t="n">
-        <v>4.329877387974269</v>
+        <v>4.630523321310447</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01819233731686955</v>
+        <v>0.01498957264025909</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8622876559967447</v>
+        <v>-0.8631729094874467</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8986320252972779</v>
+        <v>-0.8992699574331654</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9637705660526193</v>
+        <v>-0.9641251682706145</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.0415013146020093</v>
+        <v>-0.01877113541639576</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.3568166545040524</v>
+        <v>-0.3572267610485131</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.005176081202312559</v>
+        <v>-0.02026680636053962</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>47.01846770988908</v>
+        <v>43.90228327801327</v>
       </c>
       <c r="B15" t="n">
-        <v>73.70078955220932</v>
+        <v>58.34132114901365</v>
       </c>
       <c r="C15" t="n">
-        <v>38.79586026306919</v>
+        <v>38.58213326863267</v>
       </c>
       <c r="D15" t="n">
-        <v>7.943148034891912</v>
+        <v>5.104711956121347</v>
       </c>
       <c r="E15" t="n">
-        <v>4.300129557112408</v>
+        <v>4.269532945075783</v>
       </c>
       <c r="F15" t="n">
-        <v>3.069790891914518</v>
+        <v>2.891071605665733</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05337004710575644</v>
+        <v>0.06505285468990613</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.6565194439724089</v>
+        <v>-0.520879893026481</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7592591328894441</v>
+        <v>-0.6790261292225021</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.8804755212523911</v>
+        <v>-0.8155165073956762</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.02689947532746388</v>
+        <v>-0.09439287667678302</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5734556452479712</v>
+        <v>-0.6981698069632039</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.003352530666492563</v>
+        <v>-0.002497762680956639</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>45.05648595408579</v>
+        <v>94.53389597558612</v>
       </c>
       <c r="B16" t="n">
-        <v>56.29018184709804</v>
+        <v>95.12568962090398</v>
       </c>
       <c r="C16" t="n">
-        <v>39.20018933640837</v>
+        <v>39.22012798798313</v>
       </c>
       <c r="D16" t="n">
-        <v>5.000976510494143</v>
+        <v>9.794051123750478</v>
       </c>
       <c r="E16" t="n">
-        <v>4.315477696936398</v>
+        <v>4.533967360141967</v>
       </c>
       <c r="F16" t="n">
-        <v>2.99097609077681</v>
+        <v>7.526941346988982</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0602674649054396</v>
+        <v>0.00475193972301823</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6128211609105632</v>
+        <v>-0.9479351517210942</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7331144622177727</v>
+        <v>-0.96234955262583</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.860656706506958</v>
+        <v>-0.9898709220385193</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3107137071085878</v>
+        <v>-0.2859358697155722</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7179792432192494</v>
+        <v>-0.5485540088260511</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.06865148347859135</v>
+        <v>-0.1513631971960645</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>34.17813629959723</v>
+        <v>39.77353560839829</v>
       </c>
       <c r="B17" t="n">
-        <v>59.77246019445722</v>
+        <v>54.64784078624764</v>
       </c>
       <c r="C17" t="n">
-        <v>38.80449511881621</v>
+        <v>38.57504925276958</v>
       </c>
       <c r="D17" t="n">
-        <v>5.008362714926985</v>
+        <v>5.410098399915666</v>
       </c>
       <c r="E17" t="n">
-        <v>4.275211615851473</v>
+        <v>4.329384964300963</v>
       </c>
       <c r="F17" t="n">
-        <v>2.095113926611728</v>
+        <v>2.521060904675765</v>
       </c>
       <c r="G17" t="n">
-        <v>0.170955016388798</v>
+        <v>0.09452523851333716</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1217213652257349</v>
+        <v>-0.358869627831709</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4703835372561944</v>
+        <v>-0.5902598469601518</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5879369216056136</v>
+        <v>-0.7290473550538226</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.03583673722457686</v>
+        <v>-0.001684101805511065</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.647757149772817</v>
+        <v>-0.4886056468808651</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.005111592292074588</v>
+        <v>-0.0008448256462363635</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>50.05362201905453</v>
+        <v>91.95470729155535</v>
       </c>
       <c r="B18" t="n">
-        <v>73.642637433858</v>
+        <v>67.35102613395024</v>
       </c>
       <c r="C18" t="n">
-        <v>38.8300204400017</v>
+        <v>39.44156199454392</v>
       </c>
       <c r="D18" t="n">
-        <v>7.712421304279959</v>
+        <v>10.28535820863118</v>
       </c>
       <c r="E18" t="n">
-        <v>4.29714182213038</v>
+        <v>4.9592588162673</v>
       </c>
       <c r="F18" t="n">
-        <v>3.286292561110202</v>
+        <v>7.254822011504558</v>
       </c>
       <c r="G18" t="n">
-        <v>0.04229916962388322</v>
+        <v>0.005213769067134355</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7144328919747179</v>
+        <v>-0.9436345120605868</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7960566218625436</v>
+        <v>-0.9593215498670219</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.9063443578414668</v>
+        <v>-0.9887655889750864</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.01166480429733623</v>
+        <v>-0.3037420366043356</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5823591526385917</v>
+        <v>-0.5301772894523318</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.01031151853212735</v>
+        <v>-0.2030311320602465</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>48.45494634279872</v>
+        <v>74.6900851145482</v>
       </c>
       <c r="B19" t="n">
-        <v>73.70078955220932</v>
+        <v>142.9768264396641</v>
       </c>
       <c r="C19" t="n">
-        <v>38.79587083252238</v>
+        <v>38.59024808729811</v>
       </c>
       <c r="D19" t="n">
-        <v>7.943148034891912</v>
+        <v>10.73428786664798</v>
       </c>
       <c r="E19" t="n">
-        <v>4.273944522598253</v>
+        <v>4.259762707935192</v>
       </c>
       <c r="F19" t="n">
-        <v>3.183209387742294</v>
+        <v>5.248138525656785</v>
       </c>
       <c r="G19" t="n">
-        <v>0.04774780385515788</v>
+        <v>0.01053881335713231</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6856899010502003</v>
+        <v>-0.8974257793634967</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7775769872267173</v>
+        <v>-0.9263567167782359</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8936893844296028</v>
+        <v>-0.9754435842062333</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.04474772414952297</v>
+        <v>-0.01814287974461515</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5773493233337814</v>
+        <v>-0.4071668564411558</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.003354683837321483</v>
+        <v>-0.004391220369557997</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>35.33725433397092</v>
+        <v>90.45637636074508</v>
       </c>
       <c r="B20" t="n">
-        <v>58.02648307944531</v>
+        <v>142.9768264396641</v>
       </c>
       <c r="C20" t="n">
-        <v>38.85487907836326</v>
+        <v>38.66570569794722</v>
       </c>
       <c r="D20" t="n">
-        <v>5.000360992695632</v>
+        <v>10.24315949671232</v>
       </c>
       <c r="E20" t="n">
-        <v>4.027944138205369</v>
+        <v>4.638651493579812</v>
       </c>
       <c r="F20" t="n">
-        <v>2.206159255899179</v>
+        <v>7.031352474514775</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1503401282087637</v>
+        <v>0.005495957784070921</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2047395929315989</v>
+        <v>-0.9409482715508749</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5112755521555998</v>
+        <v>-0.957490608802626</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6388157962303593</v>
+        <v>-0.9880665689483565</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1585981185428452</v>
+        <v>-0.2528095020616592</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6321207553736286</v>
+        <v>-0.5195016815703087</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.01537563055520385</v>
+        <v>-0.02199799618768511</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>34.42044630442113</v>
+        <v>37.2051461190626</v>
       </c>
       <c r="B21" t="n">
-        <v>59.47443603679527</v>
+        <v>56.11979641760919</v>
       </c>
       <c r="C21" t="n">
-        <v>38.80303026604609</v>
+        <v>39.5828320023314</v>
       </c>
       <c r="D21" t="n">
-        <v>5.000797960533887</v>
+        <v>5.694520256724487</v>
       </c>
       <c r="E21" t="n">
-        <v>4.297498225915882</v>
+        <v>4.310676883236699</v>
       </c>
       <c r="F21" t="n">
-        <v>2.115277355995209</v>
+        <v>2.340775684193241</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1663706194518607</v>
+        <v>0.1221470619561944</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1399970045922832</v>
+        <v>-0.2179619093970718</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4792906095991582</v>
+        <v>-0.5176546279741454</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5992762034601924</v>
+        <v>-0.6473215683160276</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.05095410139031727</v>
+        <v>-0.03090070895450955</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.644447529441301</v>
+        <v>-0.5489993013565585</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.004813177776470749</v>
+        <v>-0.2359941338773278</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>51.00718181264735</v>
+        <v>98.25325737607093</v>
       </c>
       <c r="B22" t="n">
-        <v>64.34117915667933</v>
+        <v>69.40441579214914</v>
       </c>
       <c r="C22" t="n">
-        <v>39.0636166663117</v>
+        <v>38.59463418103657</v>
       </c>
       <c r="D22" t="n">
-        <v>5.048913962014694</v>
+        <v>7.87961170209544</v>
       </c>
       <c r="E22" t="n">
-        <v>4.221563641603074</v>
+        <v>4.431554835755994</v>
       </c>
       <c r="F22" t="n">
-        <v>3.451948512832249</v>
+        <v>7.781749055288357</v>
       </c>
       <c r="G22" t="n">
-        <v>0.03828865302221097</v>
+        <v>0.00416084297076316</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7312472002813738</v>
+        <v>-0.9534336777801674</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8074759497412655</v>
+        <v>-0.9663517326936985</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9138959315676406</v>
+        <v>-0.9912491616658902</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1007183233225462</v>
+        <v>-0.01093294923912438</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6353744537924925</v>
+        <v>-0.5750544588045053</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.05582828763672219</v>
+        <v>-0.005414642241866885</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>35.93316683983907</v>
+        <v>68.40018404232134</v>
       </c>
       <c r="B23" t="n">
-        <v>58.02648307944531</v>
+        <v>116.7787740041449</v>
       </c>
       <c r="C23" t="n">
-        <v>38.85487907836326</v>
+        <v>39.4778760195619</v>
       </c>
       <c r="D23" t="n">
-        <v>5.000366838459829</v>
+        <v>11.25395852513279</v>
       </c>
       <c r="E23" t="n">
-        <v>4.027944138205369</v>
+        <v>4.903505989932077</v>
       </c>
       <c r="F23" t="n">
-        <v>2.221052650648245</v>
+        <v>4.706586479860579</v>
       </c>
       <c r="G23" t="n">
-        <v>0.14126146472701</v>
+        <v>0.01444273150910215</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.243115551803819</v>
+        <v>-0.8673198336616802</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5305290597464891</v>
+        <v>-0.9024598050667589</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.661670742300364</v>
+        <v>-0.9655453122571173</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.04272082860209981</v>
+        <v>-0.01985411824805904</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6329319135048741</v>
+        <v>-0.3623513113015395</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.01537563055520385</v>
+        <v>-0.2115044045644428</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>36.21106266566512</v>
+        <v>40.42476290068781</v>
       </c>
       <c r="B24" t="n">
-        <v>57.14724692272191</v>
+        <v>52.40832490143313</v>
       </c>
       <c r="C24" t="n">
-        <v>38.79462014261851</v>
+        <v>38.59063468049967</v>
       </c>
       <c r="D24" t="n">
-        <v>5.001684907787056</v>
+        <v>5.104711956121347</v>
       </c>
       <c r="E24" t="n">
-        <v>4.233082976662955</v>
+        <v>4.552040167990747</v>
       </c>
       <c r="F24" t="n">
-        <v>2.275875975204984</v>
+        <v>2.545732442738161</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1369849985717232</v>
+        <v>0.08874294205452382</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2603991611193485</v>
+        <v>-0.3891662799736684</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.5393275887322205</v>
+        <v>-0.6064192176449726</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6719294920766853</v>
+        <v>-0.7459192663370464</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.1845905754130642</v>
+        <v>-0.0002843598450839787</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6199901806024644</v>
+        <v>-0.4234342468731754</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.003099897807322535</v>
+        <v>-0.004481425449923276</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>81.11582417011503</v>
+        <v>77.59917280041505</v>
       </c>
       <c r="B25" t="n">
-        <v>152.3974556654222</v>
+        <v>113.2218685598024</v>
       </c>
       <c r="C25" t="n">
-        <v>38.97562502912888</v>
+        <v>38.60170330694594</v>
       </c>
       <c r="D25" t="n">
-        <v>9.57321363892075</v>
+        <v>10.82394601249658</v>
       </c>
       <c r="E25" t="n">
-        <v>4.275123616952778</v>
+        <v>4.92932168305957</v>
       </c>
       <c r="F25" t="n">
-        <v>5.790962390314642</v>
+        <v>5.572582243657032</v>
       </c>
       <c r="G25" t="n">
-        <v>0.008030688119563966</v>
+        <v>0.009240192538120194</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.9293407293823619</v>
+        <v>-0.9081652489056762</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.9497632324372424</v>
+        <v>-0.935140760356065</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.9849151004357561</v>
+        <v>-0.9787530201860348</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.02376072581826883</v>
+        <v>-0.0890495644522088</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.480940862752341</v>
+        <v>-0.4278941062029571</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.03997355953732193</v>
+        <v>-0.007064104954053879</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>54.10319490653644</v>
+        <v>35.95455454294491</v>
       </c>
       <c r="B26" t="n">
-        <v>61.07097615144669</v>
+        <v>58.40014666794944</v>
       </c>
       <c r="C26" t="n">
-        <v>38.80284700228272</v>
+        <v>39.19784119181105</v>
       </c>
       <c r="D26" t="n">
-        <v>5.327278526398494</v>
+        <v>5.994982929294398</v>
       </c>
       <c r="E26" t="n">
-        <v>4.050862195357108</v>
+        <v>4.097524010437242</v>
       </c>
       <c r="F26" t="n">
-        <v>3.791797988987109</v>
+        <v>2.263181367429774</v>
       </c>
       <c r="G26" t="n">
-        <v>0.03094794826524346</v>
+        <v>0.1394130993330674</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.7739195106898464</v>
+        <v>-0.1340810941749015</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.8360999989693547</v>
+        <v>-0.4761239589063553</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.9314216332794597</v>
+        <v>-0.596226801272668</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.2822841726133394</v>
+        <v>-0.004066625918466241</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.5617380712668361</v>
+        <v>-0.6337269273680934</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.004775843944505491</v>
+        <v>-0.1461629447559112</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>74.55764073189707</v>
+        <v>48.45981910798088</v>
       </c>
       <c r="B27" t="n">
-        <v>181.0426782781331</v>
+        <v>60.07523563352433</v>
       </c>
       <c r="C27" t="n">
-        <v>38.8023818212998</v>
+        <v>38.73376437441831</v>
       </c>
       <c r="D27" t="n">
-        <v>11.02102053699844</v>
+        <v>5.104581384296726</v>
       </c>
       <c r="E27" t="n">
-        <v>4.138354125790317</v>
+        <v>4.851266791550523</v>
       </c>
       <c r="F27" t="n">
-        <v>5.246162496009835</v>
+        <v>3.389406363589124</v>
       </c>
       <c r="G27" t="n">
-        <v>0.01083559854173314</v>
+        <v>0.04505710503965857</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.9097248230754559</v>
+        <v>-0.6422867802211298</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.9361386892158748</v>
+        <v>-0.7508881617133832</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.9791952969203012</v>
+        <v>-0.8746458117269235</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.1362797536475925</v>
+        <v>-0.4150834182313927</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.4319507751671127</v>
+        <v>-0.6298829140258365</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.004681078954797963</v>
+        <v>-0.03787835403093867</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>83.91996959751293</v>
+        <v>38.88949593389488</v>
       </c>
       <c r="B28" t="n">
-        <v>147.2862946334263</v>
+        <v>55.12133874586927</v>
       </c>
       <c r="C28" t="n">
-        <v>38.80573701374846</v>
+        <v>38.57769787274223</v>
       </c>
       <c r="D28" t="n">
-        <v>9.977219238416174</v>
+        <v>5.561852235492985</v>
       </c>
       <c r="E28" t="n">
-        <v>4.645899546321385</v>
+        <v>4.102407968655178</v>
       </c>
       <c r="F28" t="n">
-        <v>6.15990095904474</v>
+        <v>2.457620785649611</v>
       </c>
       <c r="G28" t="n">
-        <v>0.007175001978472728</v>
+        <v>0.1030275810652425</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.9358691823380316</v>
+        <v>-0.3145338903505049</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.9540822760569058</v>
+        <v>-0.5669924319775302</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.9867014873811788</v>
+        <v>-0.7039157218940555</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.1615361198004389</v>
+        <v>-0.001996032289405497</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.5018880246278967</v>
+        <v>-0.5221991545119949</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.005364586642219074</v>
+        <v>-0.001462836973187137</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>77.76731400755764</v>
+        <v>51.08264651314376</v>
       </c>
       <c r="B29" t="n">
-        <v>192.7396467275886</v>
+        <v>86.48010822969589</v>
       </c>
       <c r="C29" t="n">
-        <v>38.80442401600614</v>
+        <v>38.59430200359457</v>
       </c>
       <c r="D29" t="n">
-        <v>9.979855212617858</v>
+        <v>7.883690017000538</v>
       </c>
       <c r="E29" t="n">
-        <v>4.341828861339784</v>
+        <v>4.251465039208495</v>
       </c>
       <c r="F29" t="n">
-        <v>5.462154970442485</v>
+        <v>3.417772587772528</v>
       </c>
       <c r="G29" t="n">
-        <v>0.009296760354394794</v>
+        <v>0.03846766178458495</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.9201911034201798</v>
+        <v>-0.6919100609481427</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.943712261380832</v>
+        <v>-0.7814031958371567</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.9823101914025412</v>
+        <v>-0.8965803807072927</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.02079799089669793</v>
+        <v>-0.004381793234830587</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.4559272583466233</v>
+        <v>-0.5735234279165771</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.005097107484415247</v>
+        <v>-0.005337134172067465</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>52.80734843133197</v>
+        <v>46.51540119773124</v>
       </c>
       <c r="B30" t="n">
-        <v>89.31945203635726</v>
+        <v>51.71251110490397</v>
       </c>
       <c r="C30" t="n">
-        <v>38.8300204400017</v>
+        <v>38.60885918444431</v>
       </c>
       <c r="D30" t="n">
-        <v>7.634568700858729</v>
+        <v>5.0708532861333</v>
       </c>
       <c r="E30" t="n">
-        <v>3.723280112858533</v>
+        <v>4.661236754013508</v>
       </c>
       <c r="F30" t="n">
-        <v>3.541778517608693</v>
+        <v>3.165735010229996</v>
       </c>
       <c r="G30" t="n">
-        <v>0.03469547172045152</v>
+        <v>0.05242627916389957</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.7561418907920493</v>
+        <v>-0.5962656155137832</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.8236739356510634</v>
+        <v>-0.7230218249023559</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.9239652513928659</v>
+        <v>-0.8529049399803265</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.08715091813301437</v>
+        <v>-0.2678090434905425</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.6006440666980504</v>
+        <v>-0.7136851946115292</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.01031151853212735</v>
+        <v>-0.008733809703672241</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>66.51209703429912</v>
+        <v>41.07676257570023</v>
       </c>
       <c r="B31" t="n">
-        <v>188.1499311632862</v>
+        <v>51.62054836375242</v>
       </c>
       <c r="C31" t="n">
-        <v>38.95591802994785</v>
+        <v>39.31431875012472</v>
       </c>
       <c r="D31" t="n">
-        <v>11.9392823688611</v>
+        <v>5.029281910457641</v>
       </c>
       <c r="E31" t="n">
-        <v>4.374615138930976</v>
+        <v>3.848593096180168</v>
       </c>
       <c r="F31" t="n">
-        <v>4.567667631905699</v>
+        <v>2.6106307759638</v>
       </c>
       <c r="G31" t="n">
-        <v>0.01634966119344675</v>
+        <v>0.08354626484959678</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.8740116155672296</v>
+        <v>-0.4174891942689279</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.9076580619732282</v>
+        <v>-0.6216954025301271</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.9677530620362279</v>
+        <v>-0.7614048236336679</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.1379563652689522</v>
+        <v>-0.03745261513483986</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.3718500027307739</v>
+        <v>-0.3980062595476911</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.03595892084151497</v>
+        <v>-0.1733410416957684</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>82.8916551907039</v>
+        <v>38.04828797254213</v>
       </c>
       <c r="B32" t="n">
-        <v>147.2862946334263</v>
+        <v>55.13081810134888</v>
       </c>
       <c r="C32" t="n">
-        <v>38.8380043459687</v>
+        <v>38.58626829409882</v>
       </c>
       <c r="D32" t="n">
-        <v>9.977219238416174</v>
+        <v>5.642046608071039</v>
       </c>
       <c r="E32" t="n">
-        <v>4.645899546321385</v>
+        <v>4.151529744502592</v>
       </c>
       <c r="F32" t="n">
-        <v>6.040553027531693</v>
+        <v>2.391271052468255</v>
       </c>
       <c r="G32" t="n">
-        <v>0.007480008330202192</v>
+        <v>0.1120153850939892</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.9335634781594687</v>
+        <v>-0.2684666104135017</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.9525357132030039</v>
+        <v>-0.5432437231037102</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.9860750094198276</v>
+        <v>-0.6772369869132587</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.1386479652090606</v>
+        <v>-0.03823642388017193</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.494206444304731</v>
+        <v>-0.5161167690708565</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.01193797101961048</v>
+        <v>-0.003462601956392836</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>37.82831408679807</v>
+        <v>37.07034538127929</v>
       </c>
       <c r="B33" t="n">
-        <v>56.29018184709804</v>
+        <v>56.04445047098601</v>
       </c>
       <c r="C33" t="n">
-        <v>38.91915168439837</v>
+        <v>38.76270034790644</v>
       </c>
       <c r="D33" t="n">
-        <v>5.000317791493432</v>
+        <v>5.694520256724487</v>
       </c>
       <c r="E33" t="n">
-        <v>4.315477696936398</v>
+        <v>4.150362770991228</v>
       </c>
       <c r="F33" t="n">
-        <v>2.361912152921404</v>
+        <v>2.314268806470522</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1162280701040922</v>
+        <v>0.1237642299773271</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3502003863718428</v>
+        <v>-0.2095371850024241</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5857877037838708</v>
+        <v>-0.5134437994024832</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.7235768698334926</v>
+        <v>-0.6422969493389683</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.05827414430968282</v>
+        <v>-0.002580317916161751</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.6362624045892311</v>
+        <v>-0.5542565301301082</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.02846901371814083</v>
+        <v>-0.04463008117816886</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>33.57038338270492</v>
+        <v>45.39077850793227</v>
       </c>
       <c r="B34" t="n">
-        <v>60.32921384356077</v>
+        <v>60.10015802572135</v>
       </c>
       <c r="C34" t="n">
-        <v>40.06063742719599</v>
+        <v>39.46398396035723</v>
       </c>
       <c r="D34" t="n">
-        <v>5.015215181341347</v>
+        <v>5.254201093618383</v>
       </c>
       <c r="E34" t="n">
-        <v>4.138039485247198</v>
+        <v>4.083212124099083</v>
       </c>
       <c r="F34" t="n">
-        <v>2.063482981701494</v>
+        <v>3.080418462737024</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1833409909117489</v>
+        <v>0.05750665118756439</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.07341175865431877</v>
+        <v>-0.5658357191708647</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4470603489372497</v>
+        <v>-0.7050075796188385</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.5575422002217996</v>
+        <v>-0.8380364449238566</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.02479133958459697</v>
+        <v>-0.2601092101971564</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.6560582160525471</v>
+        <v>-0.7070077473908478</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.09041746748557526</v>
+        <v>-0.2082629240833525</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>91.5860997540416</v>
+        <v>53.08056806723992</v>
       </c>
       <c r="B35" t="n">
-        <v>71.9361211609249</v>
+        <v>65.11602061571527</v>
       </c>
       <c r="C35" t="n">
-        <v>38.78700825898578</v>
+        <v>38.60775447765779</v>
       </c>
       <c r="D35" t="n">
-        <v>9.542439321654616</v>
+        <v>7.439078177515105</v>
       </c>
       <c r="E35" t="n">
-        <v>4.588461690312672</v>
+        <v>4.808207929120625</v>
       </c>
       <c r="F35" t="n">
-        <v>7.050311566747981</v>
+        <v>3.560174437161454</v>
       </c>
       <c r="G35" t="n">
-        <v>0.005353918676259191</v>
+        <v>0.03331037183711125</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.9500349995473443</v>
+        <v>-0.7261341709986843</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9638643311816639</v>
+        <v>-0.8039508351907358</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.9903905603148804</v>
+        <v>-0.9117861929769822</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.2754262992100781</v>
+        <v>-0.001619102309170178</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.5591545514559645</v>
+        <v>-0.5950236924370595</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.001549232366114968</v>
+        <v>-0.008476044786816656</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>72.36305937776963</v>
+        <v>54.16938651980133</v>
       </c>
       <c r="B36" t="n">
-        <v>148.0451336577155</v>
+        <v>89.24955208308332</v>
       </c>
       <c r="C36" t="n">
-        <v>38.87301707178922</v>
+        <v>38.58046183840824</v>
       </c>
       <c r="D36" t="n">
-        <v>11.14800553378973</v>
+        <v>8.496442222119088</v>
       </c>
       <c r="E36" t="n">
-        <v>4.447653225035502</v>
+        <v>4.251908668891524</v>
       </c>
       <c r="F36" t="n">
-        <v>5.037906077591773</v>
+        <v>3.798093236870983</v>
       </c>
       <c r="G36" t="n">
-        <v>0.01204249856432766</v>
+        <v>0.03112047707926661</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.9015422591271673</v>
+        <v>-0.7406879378241271</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9296954176622143</v>
+        <v>-0.8131382551661412</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.9766881294085656</v>
+        <v>-0.917586907980915</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.1170017432793944</v>
+        <v>-0.2255078945085612</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.415557099423754</v>
+        <v>-0.5930727812920751</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.0190706370654921</v>
+        <v>-0.002107762295256582</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>98.74515743397794</v>
+        <v>34.59549634024591</v>
       </c>
       <c r="B37" t="n">
-        <v>172.5673838402515</v>
+        <v>59.77228953371635</v>
       </c>
       <c r="C37" t="n">
-        <v>38.8023818212998</v>
+        <v>39.47554917221139</v>
       </c>
       <c r="D37" t="n">
-        <v>7.075422404576648</v>
+        <v>6.053403072778151</v>
       </c>
       <c r="E37" t="n">
-        <v>4.01342127505367</v>
+        <v>4.096071731042414</v>
       </c>
       <c r="F37" t="n">
-        <v>7.705638053368057</v>
+        <v>2.16273220756831</v>
       </c>
       <c r="G37" t="n">
-        <v>0.004153404682313234</v>
+        <v>0.1617298394322116</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.959696016760718</v>
+        <v>-0.02875927008610119</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.9709118559511259</v>
+        <v>-0.4255188678611065</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.9927368137132473</v>
+        <v>-0.5297618474839004</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.009899912330326515</v>
+        <v>-0.00646570090346083</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.6126332115257539</v>
+        <v>-0.6507756427304098</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.004681078954797963</v>
+        <v>-0.2109614735159913</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>54.01607432170997</v>
+        <v>38.04828797254213</v>
       </c>
       <c r="B38" t="n">
-        <v>73.22052007253207</v>
+        <v>55.13081810134888</v>
       </c>
       <c r="C38" t="n">
-        <v>38.8300204400017</v>
+        <v>38.58626829409882</v>
       </c>
       <c r="D38" t="n">
-        <v>7.634568700858729</v>
+        <v>5.642046608071039</v>
       </c>
       <c r="E38" t="n">
-        <v>3.736693901373786</v>
+        <v>4.12326578020141</v>
       </c>
       <c r="F38" t="n">
-        <v>3.662578418478494</v>
+        <v>2.391271052468255</v>
       </c>
       <c r="G38" t="n">
-        <v>0.03193164197966948</v>
+        <v>0.1120153850939892</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.7718499351246628</v>
+        <v>-0.2684666104135017</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.8343503135073563</v>
+        <v>-0.5432437231037102</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.9303562656917727</v>
+        <v>-0.6772369869132587</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.1291607628903449</v>
+        <v>-0.03823642388017193</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.6086700815296129</v>
+        <v>-0.5161167690708565</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.01031151853212735</v>
+        <v>-0.003462601956392836</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>43.94211839373354</v>
+        <v>39.0468976411419</v>
       </c>
       <c r="B39" t="n">
-        <v>59.18304659238265</v>
+        <v>54.8086729362125</v>
       </c>
       <c r="C39" t="n">
-        <v>38.80587307296206</v>
+        <v>38.57758139906036</v>
       </c>
       <c r="D39" t="n">
-        <v>5.15334454757359</v>
+        <v>5.663306939375428</v>
       </c>
       <c r="E39" t="n">
-        <v>4.221563641603074</v>
+        <v>4.102407968655178</v>
       </c>
       <c r="F39" t="n">
-        <v>2.887393959615103</v>
+        <v>2.484399555458999</v>
       </c>
       <c r="G39" t="n">
-        <v>0.06621937601255418</v>
+        <v>0.1015161775025052</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.5830164615040118</v>
+        <v>-0.3226678583083859</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.7153146535742035</v>
+        <v>-0.5712202286566014</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.8462909016932482</v>
+        <v>-0.7085487620063903</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.264632939675211</v>
+        <v>-0.04656270965607457</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.7110422404020703</v>
+        <v>-0.5162178896366082</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.005392304133799953</v>
+        <v>-0.001435659780749943</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>33.15084393648854</v>
+        <v>35.04597352231116</v>
       </c>
       <c r="B40" t="n">
-        <v>59.77246019445722</v>
+        <v>58.95226485766682</v>
       </c>
       <c r="C40" t="n">
-        <v>38.83676245103646</v>
+        <v>38.76701084286946</v>
       </c>
       <c r="D40" t="n">
-        <v>5.008362714926985</v>
+        <v>6.02825452183698</v>
       </c>
       <c r="E40" t="n">
-        <v>4.275211615851473</v>
+        <v>4.426271246503536</v>
       </c>
       <c r="F40" t="n">
-        <v>2.048496607570955</v>
+        <v>2.183109741323013</v>
       </c>
       <c r="G40" t="n">
-        <v>0.19181585645754</v>
+        <v>0.1537599985401892</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.03853188848913925</v>
+        <v>-0.06555171842071876</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4305102388451691</v>
+        <v>-0.4430272885085869</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.5354962253278515</v>
+        <v>-0.5532919532875882</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.167950633578101</v>
+        <v>-0.003621408061285288</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.6740254850627614</v>
+        <v>-0.633207032629865</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.01168497666946738</v>
+        <v>-0.04563586333620778</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>36.8915282567059</v>
+        <v>72.01032918131065</v>
       </c>
       <c r="B41" t="n">
-        <v>57.04066146283907</v>
+        <v>116.9781476876991</v>
       </c>
       <c r="C41" t="n">
-        <v>38.80280154717924</v>
+        <v>39.61063013145672</v>
       </c>
       <c r="D41" t="n">
-        <v>5.001623278111835</v>
+        <v>10.81275332747175</v>
       </c>
       <c r="E41" t="n">
-        <v>4.230241613015015</v>
+        <v>4.644663036676263</v>
       </c>
       <c r="F41" t="n">
-        <v>2.285183938615197</v>
+        <v>5.014550043344304</v>
       </c>
       <c r="G41" t="n">
-        <v>0.1278301580666738</v>
+        <v>0.01200484085168206</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.2999959300639388</v>
+        <v>-0.8858697589198805</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5595962506703299</v>
+        <v>-0.9170438906289259</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.6949367933940329</v>
+        <v>-0.9717420556656284</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.02919634370460663</v>
+        <v>-0.007999367756289528</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.6360259461413017</v>
+        <v>-0.3880735954168384</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.004766583994998217</v>
+        <v>-0.2424803640065697</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>37.64783329653259</v>
+        <v>35.04597352231116</v>
       </c>
       <c r="B42" t="n">
-        <v>56.2400551565408</v>
+        <v>59.26722867708382</v>
       </c>
       <c r="C42" t="n">
-        <v>38.92203991240873</v>
+        <v>38.76701084286946</v>
       </c>
       <c r="D42" t="n">
-        <v>5.015160258237077</v>
+        <v>6.02825452183698</v>
       </c>
       <c r="E42" t="n">
-        <v>4.217909126923633</v>
+        <v>4.426271246503536</v>
       </c>
       <c r="F42" t="n">
-        <v>2.347121129269133</v>
+        <v>2.183109741323013</v>
       </c>
       <c r="G42" t="n">
-        <v>0.1183747924629316</v>
+        <v>0.1537599985401892</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.3408957666564467</v>
+        <v>-0.06555171842071876</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.5808905414202791</v>
+        <v>-0.4430272885085869</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.7183158920275832</v>
+        <v>-0.5532919532875882</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.05081902227910489</v>
+        <v>-0.003621408061285288</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.6370535445854156</v>
+        <v>-0.633207032629865</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.02905739309676513</v>
+        <v>-0.04563586333620778</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>37.04065810039771</v>
+        <v>52.14507188238428</v>
       </c>
       <c r="B43" t="n">
-        <v>57.63624130244055</v>
+        <v>86.30872972578885</v>
       </c>
       <c r="C43" t="n">
-        <v>38.92115056049638</v>
+        <v>38.59430200359457</v>
       </c>
       <c r="D43" t="n">
-        <v>5.101471743193253</v>
+        <v>7.844365038977829</v>
       </c>
       <c r="E43" t="n">
-        <v>4.521678051366779</v>
+        <v>4.251382504544187</v>
       </c>
       <c r="F43" t="n">
-        <v>2.302234115861638</v>
+        <v>3.516354955772878</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1260066371797988</v>
+        <v>0.03564795205969738</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.308226014627862</v>
+        <v>-0.710082655618739</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.5638356980378371</v>
+        <v>-0.7930999270173286</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.6996433206863911</v>
+        <v>-0.904563490753884</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.03944025000892511</v>
+        <v>-0.0279660390844264</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.6397151053069019</v>
+        <v>-0.5802521219217671</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.02887621753732524</v>
+        <v>-0.005337134172067465</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>42.73511446684963</v>
+        <v>72.01032918131065</v>
       </c>
       <c r="B44" t="n">
-        <v>72.11693173489672</v>
+        <v>113.662225903473</v>
       </c>
       <c r="C44" t="n">
-        <v>38.8323991825026</v>
+        <v>39.61063013145672</v>
       </c>
       <c r="D44" t="n">
-        <v>5.001351727433272</v>
+        <v>10.81275332747175</v>
       </c>
       <c r="E44" t="n">
-        <v>4.275314161695479</v>
+        <v>4.644663036676263</v>
       </c>
       <c r="F44" t="n">
-        <v>2.731832568716461</v>
+        <v>5.014550043344304</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0735017005446652</v>
+        <v>0.01200484085168206</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.5471924225384218</v>
+        <v>-0.8858697589198805</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.6943500994465537</v>
+        <v>-0.9170438906289259</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.8285900303839034</v>
+        <v>-0.9717420556656284</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.05784987121956875</v>
+        <v>-0.007999367756289528</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.6978869743030857</v>
+        <v>-0.3880735954168384</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.01079610736291597</v>
+        <v>-0.2424803640065697</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>93.75054415430964</v>
+        <v>89.01225135201031</v>
       </c>
       <c r="B45" t="n">
-        <v>68.93828382047104</v>
+        <v>103.4326463715422</v>
       </c>
       <c r="C45" t="n">
-        <v>38.81192610550976</v>
+        <v>38.59032446541554</v>
       </c>
       <c r="D45" t="n">
-        <v>7.883379838564545</v>
+        <v>9.574435550956341</v>
       </c>
       <c r="E45" t="n">
-        <v>4.634924033513813</v>
+        <v>3.815751601594855</v>
       </c>
       <c r="F45" t="n">
-        <v>7.129912047438531</v>
+        <v>6.76443035750371</v>
       </c>
       <c r="G45" t="n">
-        <v>0.004922211112513707</v>
+        <v>0.00577484194101213</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.9533166316769318</v>
+        <v>-0.9382235316046084</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.9662809446552723</v>
+        <v>-0.9556833991174769</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.9912113233932115</v>
+        <v>-0.987352254624668</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.01912728737853443</v>
+        <v>-0.1088347652837041</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.5753231020525457</v>
+        <v>-0.5092122908830735</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.006625406062192639</v>
+        <v>-0.004409041930293206</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>41.69490644309572</v>
+        <v>76.56924795777741</v>
       </c>
       <c r="B46" t="n">
-        <v>55.90606986082226</v>
+        <v>96.93560083751053</v>
       </c>
       <c r="C46" t="n">
-        <v>38.80296234419502</v>
+        <v>38.66482058552076</v>
       </c>
       <c r="D46" t="n">
-        <v>5.26756983284336</v>
+        <v>10.73165976613465</v>
       </c>
       <c r="E46" t="n">
-        <v>4.151270595216389</v>
+        <v>4.354822659186628</v>
       </c>
       <c r="F46" t="n">
-        <v>2.676239464296326</v>
+        <v>5.451258024432272</v>
       </c>
       <c r="G46" t="n">
-        <v>0.08071379526236432</v>
+        <v>0.009670897469328742</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.5128393322518627</v>
+        <v>-0.9045534314479809</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.674625960491692</v>
+        <v>-0.9321711061731748</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.8111527586410124</v>
+        <v>-0.9776541116835644</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.1423694686408994</v>
+        <v>-0.05526785667671141</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.6970532154277205</v>
+        <v>-0.420555891699164</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.004799340982291202</v>
+        <v>-0.02179146995484368</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>41.64833216067824</v>
+        <v>53.92237615445384</v>
       </c>
       <c r="B47" t="n">
-        <v>55.90606986082226</v>
+        <v>82.65234690144463</v>
       </c>
       <c r="C47" t="n">
-        <v>38.80284377855148</v>
+        <v>38.68191300015027</v>
       </c>
       <c r="D47" t="n">
-        <v>5.067198950620235</v>
+        <v>8.462030925029213</v>
       </c>
       <c r="E47" t="n">
-        <v>4.299474858777104</v>
+        <v>4.694364613034959</v>
       </c>
       <c r="F47" t="n">
-        <v>2.64723219533297</v>
+        <v>3.771451550876273</v>
       </c>
       <c r="G47" t="n">
-        <v>0.08096900549715966</v>
+        <v>0.03164357102950897</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.5113056252188918</v>
+        <v>-0.7371753644163628</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.6737725450217827</v>
+        <v>-0.8108049649568464</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.8103910816774086</v>
+        <v>-0.9161112735437271</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.06984659459947956</v>
+        <v>-0.2145457978019542</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.6967632878133202</v>
+        <v>-0.591508382311541</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.004775187217622481</v>
+        <v>-0.02577970003506222</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>67.90226356623332</v>
+        <v>86.42176006441588</v>
       </c>
       <c r="B48" t="n">
-        <v>177.166711636058</v>
+        <v>111.2248053409306</v>
       </c>
       <c r="C48" t="n">
-        <v>38.81599086339629</v>
+        <v>38.60906134181957</v>
       </c>
       <c r="D48" t="n">
-        <v>11.45152205562816</v>
+        <v>10.01834952947947</v>
       </c>
       <c r="E48" t="n">
-        <v>4.905409001233791</v>
+        <v>4.491897307555152</v>
       </c>
       <c r="F48" t="n">
-        <v>4.633946439246608</v>
+        <v>6.497744582191982</v>
       </c>
       <c r="G48" t="n">
-        <v>0.01511757306970833</v>
+        <v>0.006384241424464547</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.8814879868324161</v>
+        <v>-0.9327351453109514</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.913579764287991</v>
+        <v>-0.9519597857826708</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.9702612496792646</v>
+        <v>-0.9858638682905108</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.08405460179020646</v>
+        <v>-0.1297884555837268</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.3822346436605518</v>
+        <v>-0.4907550404589631</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.007453463857824174</v>
+        <v>-0.008780979757899293</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>33.57038338270492</v>
+        <v>47.59548446929634</v>
       </c>
       <c r="B49" t="n">
-        <v>60.18753167963268</v>
+        <v>59.94531278848865</v>
       </c>
       <c r="C49" t="n">
-        <v>40.06063742719599</v>
+        <v>38.72101927081734</v>
       </c>
       <c r="D49" t="n">
-        <v>5.015215181341347</v>
+        <v>5.104581384296726</v>
       </c>
       <c r="E49" t="n">
-        <v>4.235303395984188</v>
+        <v>4.172242843558268</v>
       </c>
       <c r="F49" t="n">
-        <v>2.063482981701494</v>
+        <v>3.291391170941917</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1833409909117489</v>
+        <v>0.0481578106051679</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.07341175865431877</v>
+        <v>-0.622746841053601</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.4470603489372497</v>
+        <v>-0.7389521411528002</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.5575422002217996</v>
+        <v>-0.8655185676359316</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.02479133958459697</v>
+        <v>-0.3547171067874124</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.6560582160525471</v>
+        <v>-0.6676975544682853</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.09041746748557526</v>
+        <v>-0.03490449652404484</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>66.54392243263085</v>
+        <v>47.28121576480352</v>
       </c>
       <c r="B50" t="n">
-        <v>58.12508870099743</v>
+        <v>60.07523563352433</v>
       </c>
       <c r="C50" t="n">
-        <v>38.7936154240043</v>
+        <v>38.66393084041825</v>
       </c>
       <c r="D50" t="n">
-        <v>5.552525124719214</v>
+        <v>5.008947430446419</v>
       </c>
       <c r="E50" t="n">
-        <v>4.552444950153538</v>
+        <v>4.711699407330872</v>
       </c>
       <c r="F50" t="n">
-        <v>4.820572284359836</v>
+        <v>3.243698766394552</v>
       </c>
       <c r="G50" t="n">
-        <v>0.01495907274500384</v>
+        <v>0.04933170743533786</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.8762825934299351</v>
+        <v>-0.6153161465920045</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.9104341338938029</v>
+        <v>-0.7344613517806832</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.9688935435660994</v>
+        <v>-0.862015088015382</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.1765577014609963</v>
+        <v>-0.306140161099501</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.691855769489329</v>
+        <v>-0.6814468102898458</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.002895220160059846</v>
+        <v>-0.02158386276425978</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>42.89576650175994</v>
+        <v>44.91208552127326</v>
       </c>
       <c r="B51" t="n">
-        <v>66.52820192977434</v>
+        <v>59.69518701780804</v>
       </c>
       <c r="C51" t="n">
-        <v>38.79602690051554</v>
+        <v>39.33017193470753</v>
       </c>
       <c r="D51" t="n">
-        <v>5.000494920600477</v>
+        <v>5.104581384296726</v>
       </c>
       <c r="E51" t="n">
-        <v>4.275314161695479</v>
+        <v>4.122359144065646</v>
       </c>
       <c r="F51" t="n">
-        <v>2.762314291682651</v>
+        <v>3.008741364335886</v>
       </c>
       <c r="G51" t="n">
-        <v>0.07243039585750818</v>
+        <v>0.05977892926546027</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.5522386531632349</v>
+        <v>-0.5520530819918741</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6972881965691713</v>
+        <v>-0.6969792272342442</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.8311247254677162</v>
+        <v>-0.8312186946774371</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.1394272496184588</v>
+        <v>-0.1806980625826494</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.7045286390728224</v>
+        <v>-0.7041655077825599</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.003386477445204823</v>
+        <v>-0.1770401180984237</v>
       </c>
     </row>
   </sheetData>
